--- a/output/xlsx/matriz_diseno_20261007.xlsx
+++ b/output/xlsx/matriz_diseno_20261007.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trazabilidad Diseño'!$A$1:$J$63</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Trazabilidad Diseño'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +29,58 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF212529"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF0F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,14 +88,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFC8D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFC8D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFC8D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFC8D6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="6" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -416,3295 +491,3296 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>HU origen</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Código requisito</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Nombre del requisito</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Diseño</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Elementos de Diseño</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Estado de trazabilidad</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Estado de Diseño</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>RF-001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Registrar ejemplar asociado a libro y sucursal</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un ejemplar asociándolo a un libro y sucursal existentes, asignando automáticamente el estado inicial "disponible" y registrando su condición física.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>ED-01, ED-02, ED-04</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="44.5" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>RF-002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Generar código de identificación automático</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá generar automáticamente el código de identificación del ejemplar con el formato bib-{sucursal}-{categoría}-{secuencial}.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>ED-02</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Requiere revisión</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con confianza insuficiente para confirmarla.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>RF-003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Dar de baja un ejemplar registrando el motivo</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir dar de baja un ejemplar registrando el motivo correspondiente.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>ED-02</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>RF-004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Impedir dar de baja un ejemplar prestado o dado de baja</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá impedir dar de baja un ejemplar que se encuentre actualmente prestado o ya dado de baja.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>DIS-002</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>ED-06</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>RF-005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Consultar ejemplares asociados a un libro específico</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar los ejemplares asociados a un libro específico con su estado actual.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>DIS-002</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>ED-06, ED-08</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>RF-006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>El libro y la sucursal deben existir previamente en el sistema</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el libro y la sucursal deben existir previamente en el sistema.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>DIS-004</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>ED-14</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>RF-007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>DIS-003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>ED-10</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>RF-007</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>El código de ejemplar debe ser único en todo el sistema</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el código de ejemplar debe ser único en todo el sistema.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>DIS-004</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>ED-14</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>HU-002 – HU-002 - Registro y gestión de ejemplares</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>RF-008</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>El secuencial del código se genera automáticamente por sucursal y categoría</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el secuencial del código se genera automáticamente por sucursal y categoría.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>DIS-003</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>ED-10</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="31" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>RF-009</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Registrar préstamo de ejemplar a lector</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un préstamo seleccionando un ejemplar disponible y un lector.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>DIS-005</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>ED-15, ED-16, ED-17</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>CORREGIR</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="44.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>RF-010</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Verificar estado disponible del ejemplar</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el ejemplar se encuentre en estado disponible antes de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RF-011</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Verificar que el lector esté activo</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector esté activo en el sistema.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>RNF-001</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>ED-02</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>RNF-001</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>DIS-002</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>ED-06</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>RNF-001</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Verificar límite máximo de préstamos activos del lector</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el lector no haya alcanzado el límite máximo de préstamos activos simultáneos.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>DIS-003</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ED-10</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>RF-012</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Impedir préstamo cuando el lector tenga préstamos vencidos</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá impedir el préstamo cuando el lector tenga préstamos vencidos sin devolver.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>RF-013</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Calcular fecha de devolución esperada</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá calcular automáticamente la fecha de devolución esperada según los días configurados.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44.5" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>RF-014</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Cambiar estado del ejemplar a 'prestado'</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá cambiar el estado del ejemplar a "prestado" inmediatamente después de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="31" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>RF-015</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Registrar bibliotecario que realizó la operación</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá registrar el bibliotecario que realizó la operación.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>RF-016</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Solo los bibliotecarios y administradores pueden registrar préstamos</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá solo los bibliotecarios y administradores pueden registrar préstamos.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>RF-017</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Un lector puede tener como máximo 3 préstamos activos simultáneamente</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá un lector puede tener como máximo 3 préstamos activos simultáneamente.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>RNF-002</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>ED-02</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="31" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>RNF-002</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>DIS-002</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>ED-06</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="31" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>RNF-002</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>El plazo máximo de préstamo es de 15 días</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el plazo máximo de préstamo es de 15 días.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>DIS-003</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>ED-10</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="31" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>RF-018</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>No se permiten préstamos a lectores con devoluciones pendientes vencidas</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá no se permiten préstamos a lectores con devoluciones pendientes vencidas.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="98.5" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>HU-003 – HU-003 - Préstamo de ejemplares</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>RF-019</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>El identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el identificador del lector se obtiene del sistema, no de un dato proporcionado por el cliente. El préstamo debe quedar asociado al bibliotecario que realizó la operación para trazabilidad. La disponibilidad del ejemplar debe verificarse inmediatamente antes de registrar el préstamo.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="31" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>RF-020</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Buscar libros por término, categoría o sucursal</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir buscar libros por título, autor o isbn utilizando un término de búsqueda.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44.5" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>RF-021</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Filtrar resultados por categoría y sucursal</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir filtrar los resultados por categoría del libro y por sucursal con ejemplares disponibles.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44.5" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>RF-022</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mostrar cantidad de ejemplares disponibles</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar la cantidad de ejemplares disponibles de cada libro en los resultados de búsqueda.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="31" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>RF-023</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Paginar resultados de búsqueda</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá paginar los resultados de búsqueda cuando excedan 20 registros.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>RF-024</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Consultar disponibilidad detallada por sucursal</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar la disponibilidad detallada de un libro mostrando por cada sucursal el total de ejemplares y la cantidad disponible.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44.5" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>RF-025</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá los resultados deben mostrar únicamente libros activos con al menos un ejemplar registrado.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44.5" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>RNF-003</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>DIS-001</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>ED-02</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" ht="44.5" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>RNF-003</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>DIS-002</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>ED-06, ED-08</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" ht="44.5" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>RNF-003</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>DIS-003</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>ED-10</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J36" s="1" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="44.5" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>RNF-003</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la consulta de disponibilidad debe reflejar el estado actual de los ejemplares en tiempo real.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>DIS-005</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>ED-16, ED-17</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>CORREGIR</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>RF-026</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>La búsqueda utiliza coincidencia parcial para permitir resultados aproximados</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la búsqueda utiliza coincidencia parcial para permitir resultados aproximados.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>HU-004 – HU-004 - Búsqueda en catálogo</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>RNF-004</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>No funcional</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Disponibilidad de información en tiempo real</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la búsqueda utiliza coincidencia parcial (ilike) para permitir resultados aproximados. La disponibilidad se calcula en tiempo real consultando el estado actual de los ejemplares.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>DIS-004</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>ED-13</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Cubierto en Diseño</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>CONFORME CON MEJORAS</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Relación identificada con evidencia suficiente.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" ht="31" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>RF-027</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Registrar la devolución de un ejemplar prestado</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar la devolución de un ejemplar prestado.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>RF-028</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Verificar existencia de préstamo activo</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que exista un préstamo activo relacionado con el ejemplar.</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>RF-029</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Actualizar información del préstamo después de la devolución</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá actualizar la información del préstamo después de la devolución.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>RF-030</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Mostrar mensaje de devolución registrada</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar un mensaje cuando la devolución haya sido registrada.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>RF-031</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Continuar proceso con datos correctos</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>RF-032</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>El ejemplar debe existir en el sistema</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el ejemplar debe existir en el sistema.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>RF-033</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>La devolución debe corresponder a un préstamo registrado</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá la devolución debe corresponder a un préstamo registrado.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="71.5" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>HU-005 – HU-005 - Devolución de ejemplares</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>RF-034</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá todavía no se ha definido qué información específica debe actualizarse al registrar la devolución, cómo se manejarán las devoluciones realizadas fuera de plazo ni qué información deberá conservarse como evidencia de la operación.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>RF-035</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Solicitar transferencia de ejemplar disponible</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir solicitar la transferencia de un ejemplar disponible.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>RF-036</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Verificar disponibilidad del ejemplar</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá verificar que el ejemplar se encuentre disponible.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>RF-037</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Registrar sucursal de origen y destino</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá registrar la sucursal de origen y la sucursal de destino.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>RF-038</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Permitir continuar con el proceso cuando los datos sean correctos</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir continuar con el proceso cuando los datos sean correctos.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>RF-039</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>El ejemplar debe estar disponible</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá el ejemplar debe estar disponible.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>RF-040</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Las sucursales de origen y destino deben ser diferentes</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá las sucursales de origen y destino deben ser diferentes.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="71.5" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>HU-006 – HU-006 - Transferencia entre sucursales</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>RF-041</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá todavía debe definirse qué roles específicos pueden solicitar, autorizar y recibir transferencias. No se ha definido el flujo completo de estados de la transferencia ni qué operaciones deben registrarse para auditoría.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44.5" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>RF-042</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Registrar un libro con datos bibliográficos</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir registrar un libro con título, autor, isbn, editorial, año de publicación y categoría.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44.5" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>RF-043</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Validar formato y unicidad de isbn</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá validar que el isbn sea único en el sistema y tenga un formato correcto (isbn-10 o isbn-13).</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="31" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>RF-044</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Modificar la información bibliográfica de un libro existente</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá permitir modificar la información bibliográfica de un libro existente.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="31" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>RF-045</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Consultar libros aplicando filtros por título, autor y categoría</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá permitir consultar libros aplicando filtros por título, autor y categoría.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="31" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>RF-046</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Mostrar la cantidad de ejemplares asociados al consultar un libro</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá mostrar la cantidad de ejemplares asociados al consultar un libro.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="31" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>RF-047</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Paginar los resultados de la consulta cuando existan más de 20 libros</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá paginar los resultados de la consulta cuando existan más de 20 libros.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="31" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>RF-048</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>La categoría del libro debe pertenecer al conjunto predefinido del sistema</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá la categoría del libro debe pertenecer al conjunto predefinido del sistema.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="31" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>RF-049</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>No se permite registrar dos libros con el mismo ISBN</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>El sistema deberá no se permite registrar dos libros con el mismo ISBN.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="31" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>HU-001 – HU-001 - Gestión de libros</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>RF-050</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Funcional</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>El libro debe estar registrado antes de poder crear ejemplares físicos asociados</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>El sistema deberá el libro debe estar registrado antes de poder crear ejemplares físicos asociados.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>No evaluado</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>No evaluado</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>No se evaluó este requisito en ningún Issue de Diseño.</t>
         </is>
@@ -3713,69 +3789,71 @@
   </sheetData>
   <autoFilter ref="A1:J63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>requisitos_totales</t>
         </is>
       </c>
-      <c r="B1" t="n">
+      <c r="B1" s="7" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>cubiertos</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="7" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>pendientes_relacion</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>requieren_revision</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>no_evaluados</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="7" t="n">
         <v>41</v>
       </c>
     </row>
